--- a/event_feedback_forms/012_festival_experience_feedback--event_feedback_forms.xlsx
+++ b/event_feedback_forms/012_festival_experience_feedback--event_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>assigned_to_1</t>
+          <t>assigned to 1</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>assigned_to_2</t>
+          <t>assigned to 2</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>assigned_to_3</t>
+          <t>assigned to 3</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>assigned_to_4</t>
+          <t>assigned to 4</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>assigned_to_5</t>
+          <t>assigned to 5</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>assigned_to_6</t>
+          <t>assigned to 6</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>assigned_to_7</t>
+          <t>assigned to 7</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>assigned_to_8</t>
+          <t>assigned to 8</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>assigned_to_9</t>
+          <t>assigned to 9</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>assigned_to_10</t>
+          <t>assigned to 10</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>assigned_to_11</t>
+          <t>assigned to 11</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>assigned_to_12</t>
+          <t>assigned to 12</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>assigned_to_13</t>
+          <t>assigned to 13</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>assigned_to_14</t>
+          <t>assigned to 14</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>assigned_to_15</t>
+          <t>assigned to 15</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>favorite_food_1</t>
+          <t>favorite food 1</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>favorite_food_2</t>
+          <t>favorite food 2</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>favorite_food_3</t>
+          <t>favorite food 3</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>favorite_food_4</t>
+          <t>favorite food 4</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>favorite_food_5</t>
+          <t>favorite food 5</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>favorite_food_6</t>
+          <t>favorite food 6</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>favorite_food_7</t>
+          <t>favorite food 7</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>favorite_food_8</t>
+          <t>favorite food 8</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>favorite_food_9</t>
+          <t>favorite food 9</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>favorite_food_10</t>
+          <t>favorite food 10</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>favorite_band_1</t>
+          <t>favorite band 1</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>favorite_band_2</t>
+          <t>favorite band 2</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>favorite_band_3</t>
+          <t>favorite band 3</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>favorite_band_4</t>
+          <t>favorite band 4</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>favorite_band_5</t>
+          <t>favorite band 5</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>favorite_band_6</t>
+          <t>favorite band 6</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>favorite_band_7</t>
+          <t>favorite band 7</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>favorite_band_8</t>
+          <t>favorite band 8</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>favorite_band_9</t>
+          <t>favorite band 9</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>favorite_band_10</t>
+          <t>favorite band 10</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>assigned_to_1</t>
+          <t>assigned to 1</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>assigned_to_2</t>
+          <t>assigned to 2</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>assigned_to_3</t>
+          <t>assigned to 3</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>assigned_to_4</t>
+          <t>assigned to 4</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>assigned_to_5</t>
+          <t>assigned to 5</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>assigned_to_6</t>
+          <t>assigned to 6</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>assigned_to_7</t>
+          <t>assigned to 7</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>assigned_to_8</t>
+          <t>assigned to 8</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>assigned_to_9</t>
+          <t>assigned to 9</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>assigned_to_10</t>
+          <t>assigned to 10</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>assigned_to_11</t>
+          <t>assigned to 11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>assigned_to_12</t>
+          <t>assigned to 12</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>assigned_to_13</t>
+          <t>assigned to 13</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>assigned_to_14</t>
+          <t>assigned to 14</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>assigned_to_15</t>
+          <t>assigned to 15</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>assigned_to_16</t>
+          <t>assigned to 16</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>assigned_to_17</t>
+          <t>assigned to 17</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>assigned_to_18</t>
+          <t>assigned to 18</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>assigned_to_19</t>
+          <t>assigned to 19</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>assigned_to_20</t>
+          <t>assigned to 20</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>submitted_by_1</t>
+          <t>submitted by 1</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>submitted_by_2</t>
+          <t>submitted by 2</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>submitted_by_3</t>
+          <t>submitted by 3</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>submitted_by_4</t>
+          <t>submitted by 4</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>submitted_by_5</t>
+          <t>submitted by 5</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>submitted_by_6</t>
+          <t>submitted by 6</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>submitted_by_7</t>
+          <t>submitted by 7</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>submitted_by_8</t>
+          <t>submitted by 8</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>submitted_by_9</t>
+          <t>submitted by 9</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>submitted_by_10</t>
+          <t>submitted by 10</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>submitted_by_11</t>
+          <t>submitted by 11</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>submitted_by_12</t>
+          <t>submitted by 12</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>submitted_by_13</t>
+          <t>submitted by 13</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>submitted_by_14</t>
+          <t>submitted by 14</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>submitted_by_15</t>
+          <t>submitted by 15</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>submitted_by_16</t>
+          <t>submitted by 16</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>submitted_by_17</t>
+          <t>submitted by 17</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>submitted_by_18</t>
+          <t>submitted by 18</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>submitted_by_19</t>
+          <t>submitted by 19</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>submitted_by_20</t>
+          <t>submitted by 20</t>
         </is>
       </c>
     </row>
